--- a/Datos Tesis Upstream/Computacion Emergente/2526-1/Particip emergente 2526-1.xlsx
+++ b/Datos Tesis Upstream/Computacion Emergente/2526-1/Particip emergente 2526-1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelsoncarrillo/Downloads/tesis-prediccion-participacion/Datos Tesis Upstream/Computacion Emergente/2526-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{608D3627-08AF-174E-BC7B-A96031D2DC04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390584C7-5FD9-164B-8960-0877DD43384E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15980" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Intervenciones" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="126">
   <si>
     <t>Sem 1</t>
   </si>
@@ -988,7 +988,10 @@
     <t>Computación Emergente</t>
   </si>
   <si>
-    <t>2526-2</t>
+    <t>2526-1</t>
+  </si>
+  <si>
+    <t>carnet</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1001,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\ mmm"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1099,6 +1102,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -1158,7 +1169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1190,10 +1201,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1219,6 +1226,22 @@
     <xf numFmtId="9" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1563,20 +1586,20 @@
     <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" ht="15">
       <c r="B1" s="1"/>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="13" t="s">
+      <c r="D1" s="24"/>
+      <c r="E1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="24"/>
+      <c r="G1" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="14"/>
+      <c r="H1" s="24"/>
       <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1586,10 +1609,10 @@
       <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="M1" s="14"/>
+      <c r="M1" s="24"/>
       <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1652,7 +1675,7 @@
       <c r="P2" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="Q2" s="22" t="s">
+      <c r="Q2" s="20" t="s">
         <v>122</v>
       </c>
       <c r="R2" s="6" t="s">
@@ -1695,7 +1718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" ht="15">
       <c r="A4" s="12" t="s">
         <v>16</v>
       </c>
@@ -1820,7 +1843,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" ht="15">
       <c r="A7" s="12" t="s">
         <v>19</v>
       </c>
@@ -1865,7 +1888,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" ht="15">
       <c r="A8" s="12" t="s">
         <v>20</v>
       </c>
@@ -1898,7 +1921,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" ht="15">
       <c r="A9" s="12" t="s">
         <v>21</v>
       </c>
@@ -1939,7 +1962,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" ht="15">
       <c r="A10" s="12" t="s">
         <v>22</v>
       </c>
@@ -1976,7 +1999,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" ht="15">
       <c r="A11" s="12" t="s">
         <v>23</v>
       </c>
@@ -2068,7 +2091,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" ht="15">
       <c r="A13" s="12" t="s">
         <v>25</v>
       </c>
@@ -2101,7 +2124,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" ht="15">
       <c r="A14" s="12" t="s">
         <v>26</v>
       </c>
@@ -2140,7 +2163,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" ht="15">
       <c r="A15" s="12" t="s">
         <v>27</v>
       </c>
@@ -2185,7 +2208,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" ht="15">
       <c r="A16" s="12" t="s">
         <v>28</v>
       </c>
@@ -2286,7 +2309,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" ht="15">
       <c r="A19" s="12" t="s">
         <v>31</v>
       </c>
@@ -2370,7 +2393,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" ht="15">
       <c r="A21" s="12" t="s">
         <v>33</v>
       </c>
@@ -2458,7 +2481,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" ht="15">
       <c r="A23" s="12" t="s">
         <v>35</v>
       </c>
@@ -2553,7 +2576,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" ht="15">
       <c r="A26" s="12" t="s">
         <v>38</v>
       </c>
@@ -2584,7 +2607,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" ht="15">
       <c r="A27" s="12" t="s">
         <v>39</v>
       </c>
@@ -2617,7 +2640,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" ht="15">
       <c r="A28" s="12" t="s">
         <v>40</v>
       </c>
@@ -2713,7 +2736,7 @@
       </c>
     </row>
     <row r="31" spans="1:19" ht="15.75" customHeight="1">
-      <c r="R31" s="25"/>
+      <c r="R31" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -2761,30 +2784,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AC34"/>
+  <dimension ref="A1:AD34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="4" width="16" customWidth="1"/>
-    <col min="5" max="28" width="9" customWidth="1"/>
+    <col min="1" max="5" width="16" customWidth="1"/>
+    <col min="6" max="29" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29">
+    <row r="1" spans="1:30">
       <c r="A1" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="19" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:30">
       <c r="A2" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="19" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:29">
+    <row r="3" spans="1:30">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -2792,1159 +2815,1304 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:29">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:30">
+      <c r="A5" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="E5" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="F5" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="24"/>
+      <c r="H5" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14" t="s">
+      <c r="I5" s="24"/>
+      <c r="J5" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14" t="s">
+      <c r="K5" s="24"/>
+      <c r="L5" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14" t="s">
+      <c r="M5" s="24"/>
+      <c r="N5" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14" t="s">
+      <c r="O5" s="24"/>
+      <c r="P5" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="P5" s="14"/>
-      <c r="Q5" s="14" t="s">
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="R5" s="14"/>
-      <c r="S5" s="14" t="s">
+      <c r="S5" s="24"/>
+      <c r="T5" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="T5" s="14"/>
-      <c r="U5" s="14" t="s">
+      <c r="U5" s="24"/>
+      <c r="V5" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="V5" s="14"/>
-      <c r="W5" s="14" t="s">
+      <c r="W5" s="24"/>
+      <c r="X5" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="X5" s="14"/>
-      <c r="Y5" s="14" t="s">
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14" t="s">
+      <c r="AA5" s="24"/>
+      <c r="AB5" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AB5" s="14"/>
-    </row>
-    <row r="6" spans="1:29">
-      <c r="A6" s="14"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="21" t="s">
+      <c r="AC5" s="24"/>
+    </row>
+    <row r="6" spans="1:30">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="G6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="H6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="I6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="J6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="K6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="L6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="M6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="M6" s="21" t="s">
+      <c r="N6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="N6" s="21" t="s">
+      <c r="O6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="O6" s="21" t="s">
+      <c r="P6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="P6" s="21" t="s">
+      <c r="Q6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="Q6" s="21" t="s">
+      <c r="R6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="R6" s="21" t="s">
+      <c r="S6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="S6" s="21" t="s">
+      <c r="T6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="T6" s="21" t="s">
+      <c r="U6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="U6" s="21" t="s">
+      <c r="V6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="V6" s="21" t="s">
+      <c r="W6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="W6" s="21" t="s">
+      <c r="X6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="X6" s="21" t="s">
+      <c r="Y6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="Y6" s="21" t="s">
+      <c r="Z6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="Z6" s="21" t="s">
+      <c r="AA6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="AA6" s="21" t="s">
+      <c r="AB6" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="AB6" s="21" t="s">
+      <c r="AC6" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="AC6" s="21"/>
-    </row>
-    <row r="7" spans="1:29" ht="14">
+      <c r="AD6" s="19"/>
+    </row>
+    <row r="7" spans="1:30" ht="14">
       <c r="A7">
         <v>1</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C7" t="s">
         <v>63</v>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="13">
         <v>26739759</v>
       </c>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19">
-        <v>1</v>
-      </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
-      <c r="J7" s="19"/>
-      <c r="K7" s="19"/>
-      <c r="N7" s="19"/>
-      <c r="O7" s="19"/>
-      <c r="Q7" s="19"/>
-      <c r="R7" s="19"/>
-      <c r="S7" s="19"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="19"/>
-      <c r="Y7" s="23"/>
-    </row>
-    <row r="8" spans="1:29" ht="14">
+      <c r="E7" s="26" t="inlineStr">
+        <is>
+          <t>20201130042</t>
+        </is>
+      </c>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17">
+        <v>1</v>
+      </c>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="O7" s="17"/>
+      <c r="P7" s="17"/>
+      <c r="R7" s="17"/>
+      <c r="S7" s="17"/>
+      <c r="T7" s="17"/>
+      <c r="W7" s="17"/>
+      <c r="X7" s="17"/>
+      <c r="Z7" s="21"/>
+    </row>
+    <row r="8" spans="1:30" ht="14">
       <c r="A8">
         <v>2</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="16" t="s">
         <v>64</v>
       </c>
       <c r="C8" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="14">
         <v>30612950</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20">
-        <v>1</v>
-      </c>
-      <c r="H8" s="20">
-        <v>1</v>
-      </c>
-      <c r="I8" s="20">
-        <v>1</v>
-      </c>
-      <c r="J8" s="20">
-        <v>1</v>
-      </c>
-      <c r="K8" s="20">
-        <v>1</v>
-      </c>
-      <c r="N8" s="20">
-        <v>1</v>
-      </c>
-      <c r="O8" s="20">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="20">
-        <v>1</v>
-      </c>
-      <c r="R8" s="20">
-        <v>1</v>
-      </c>
-      <c r="S8" s="20">
-        <v>1</v>
-      </c>
-      <c r="V8" s="20">
-        <v>1</v>
-      </c>
-      <c r="W8" s="20">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="14">
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>20231110803</t>
+        </is>
+      </c>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18">
+        <v>1</v>
+      </c>
+      <c r="I8" s="18">
+        <v>1</v>
+      </c>
+      <c r="J8" s="18">
+        <v>1</v>
+      </c>
+      <c r="K8" s="18">
+        <v>1</v>
+      </c>
+      <c r="L8" s="18">
+        <v>1</v>
+      </c>
+      <c r="O8" s="18">
+        <v>1</v>
+      </c>
+      <c r="P8" s="18">
+        <v>1</v>
+      </c>
+      <c r="R8" s="18">
+        <v>1</v>
+      </c>
+      <c r="S8" s="18">
+        <v>1</v>
+      </c>
+      <c r="T8" s="18">
+        <v>1</v>
+      </c>
+      <c r="W8" s="18">
+        <v>1</v>
+      </c>
+      <c r="X8" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="14">
       <c r="A9">
         <v>3</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="15" t="s">
         <v>66</v>
       </c>
       <c r="C9" t="s">
         <v>67</v>
       </c>
-      <c r="D9" s="15">
+      <c r="D9" s="13">
         <v>25947729</v>
       </c>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-      <c r="I9" s="19"/>
-      <c r="J9" s="19">
-        <v>1</v>
-      </c>
-      <c r="K9" s="19"/>
-      <c r="N9" s="19"/>
-      <c r="O9" s="19"/>
-      <c r="Q9" s="19"/>
-      <c r="R9" s="19"/>
-      <c r="S9" s="19"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="19"/>
-      <c r="Y9" s="23"/>
-    </row>
-    <row r="10" spans="1:29" ht="14">
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>20171111081</t>
+        </is>
+      </c>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17">
+        <v>1</v>
+      </c>
+      <c r="L9" s="17"/>
+      <c r="O9" s="17"/>
+      <c r="P9" s="17"/>
+      <c r="R9" s="17"/>
+      <c r="S9" s="17"/>
+      <c r="T9" s="17"/>
+      <c r="W9" s="17"/>
+      <c r="X9" s="17"/>
+      <c r="Z9" s="21"/>
+    </row>
+    <row r="10" spans="1:30" ht="14">
       <c r="A10">
         <v>4</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="16" t="s">
         <v>68</v>
       </c>
       <c r="C10" t="s">
         <v>69</v>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="14">
         <v>30124314</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20">
-        <v>1</v>
-      </c>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="N10" s="20">
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>20211110346</t>
+        </is>
+      </c>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18">
+        <v>1</v>
+      </c>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="O10" s="18">
         <v>2</v>
       </c>
-      <c r="O10" s="20"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="V10" s="20"/>
-      <c r="W10" s="20"/>
-      <c r="Y10" s="24"/>
-    </row>
-    <row r="11" spans="1:29" ht="14">
+      <c r="P10" s="18"/>
+      <c r="R10" s="18"/>
+      <c r="S10" s="18"/>
+      <c r="T10" s="18"/>
+      <c r="W10" s="18"/>
+      <c r="X10" s="18"/>
+      <c r="Z10" s="22"/>
+    </row>
+    <row r="11" spans="1:30" ht="14">
       <c r="A11">
         <v>5</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="15" t="s">
         <v>70</v>
       </c>
       <c r="C11" t="s">
         <v>71</v>
       </c>
-      <c r="D11" s="15">
+      <c r="D11" s="13">
         <v>30673633</v>
       </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19">
-        <v>1</v>
-      </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19">
-        <v>1</v>
-      </c>
-      <c r="I11" s="19">
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>20231110176</t>
+        </is>
+      </c>
+      <c r="F11" s="17"/>
+      <c r="G11" s="17">
+        <v>1</v>
+      </c>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17">
+        <v>1</v>
+      </c>
+      <c r="J11" s="17">
         <v>2</v>
       </c>
-      <c r="J11" s="19">
-        <v>1</v>
-      </c>
-      <c r="K11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="19">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19">
-        <v>1</v>
-      </c>
-      <c r="S11" s="19"/>
-      <c r="V11" s="19">
-        <v>1</v>
-      </c>
-      <c r="W11" s="19"/>
-      <c r="Y11" s="23"/>
-    </row>
-    <row r="12" spans="1:29" ht="14">
+      <c r="K11" s="17">
+        <v>1</v>
+      </c>
+      <c r="L11" s="17"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="17">
+        <v>1</v>
+      </c>
+      <c r="R11" s="17"/>
+      <c r="S11" s="17">
+        <v>1</v>
+      </c>
+      <c r="T11" s="17"/>
+      <c r="W11" s="17">
+        <v>1</v>
+      </c>
+      <c r="X11" s="17"/>
+      <c r="Z11" s="21"/>
+    </row>
+    <row r="12" spans="1:30" ht="14">
       <c r="A12">
         <v>6</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="16" t="s">
         <v>72</v>
       </c>
       <c r="C12" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="14">
         <v>30346847</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20">
-        <v>1</v>
-      </c>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20"/>
-      <c r="V12" s="20"/>
-      <c r="W12" s="20"/>
-      <c r="Y12" s="24"/>
-    </row>
-    <row r="13" spans="1:29" ht="14">
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>20221110200</t>
+        </is>
+      </c>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18">
+        <v>1</v>
+      </c>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="18"/>
+      <c r="R12" s="18"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="18"/>
+      <c r="W12" s="18"/>
+      <c r="X12" s="18"/>
+      <c r="Z12" s="22"/>
+    </row>
+    <row r="13" spans="1:30" ht="14">
       <c r="A13">
         <v>7</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="15" t="s">
         <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="13">
         <v>27027053</v>
       </c>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19">
-        <v>1</v>
-      </c>
-      <c r="K13" s="19">
-        <v>1</v>
-      </c>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="19">
-        <v>1</v>
-      </c>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="V13" s="19">
-        <v>1</v>
-      </c>
-      <c r="W13" s="19"/>
-      <c r="Y13" s="23"/>
-    </row>
-    <row r="14" spans="1:29" ht="14">
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>20181110134</t>
+        </is>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="17">
+        <v>1</v>
+      </c>
+      <c r="L13" s="17">
+        <v>1</v>
+      </c>
+      <c r="O13" s="17"/>
+      <c r="P13" s="17">
+        <v>1</v>
+      </c>
+      <c r="R13" s="17">
+        <v>1</v>
+      </c>
+      <c r="S13" s="17"/>
+      <c r="T13" s="17"/>
+      <c r="W13" s="17">
+        <v>1</v>
+      </c>
+      <c r="X13" s="17"/>
+      <c r="Z13" s="21"/>
+    </row>
+    <row r="14" spans="1:30" ht="14">
       <c r="A14">
         <v>8</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="16" t="s">
         <v>76</v>
       </c>
       <c r="C14" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="14">
         <v>30085424</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20">
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>20211110365</t>
+        </is>
+      </c>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18">
         <v>2</v>
       </c>
-      <c r="K14" s="20">
-        <v>1</v>
-      </c>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-      <c r="Q14" s="20">
-        <v>1</v>
-      </c>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="20"/>
-      <c r="Y14" s="24"/>
-    </row>
-    <row r="15" spans="1:29" ht="14">
+      <c r="L14" s="18">
+        <v>1</v>
+      </c>
+      <c r="O14" s="18"/>
+      <c r="P14" s="18"/>
+      <c r="R14" s="18">
+        <v>1</v>
+      </c>
+      <c r="S14" s="18"/>
+      <c r="T14" s="18"/>
+      <c r="W14" s="18"/>
+      <c r="X14" s="18"/>
+      <c r="Z14" s="22"/>
+    </row>
+    <row r="15" spans="1:30" ht="14">
       <c r="A15">
         <v>9</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="15" t="s">
         <v>78</v>
       </c>
       <c r="C15" t="s">
         <v>79</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="13">
         <v>30124807</v>
       </c>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19">
-        <v>1</v>
-      </c>
-      <c r="G15" s="19">
-        <v>1</v>
-      </c>
-      <c r="H15" s="19">
-        <v>1</v>
-      </c>
-      <c r="I15" s="19">
-        <v>1</v>
-      </c>
-      <c r="J15" s="19">
-        <v>1</v>
-      </c>
-      <c r="K15" s="19">
-        <v>1</v>
-      </c>
-      <c r="N15" s="19">
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>20231110194</t>
+        </is>
+      </c>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17">
+        <v>1</v>
+      </c>
+      <c r="H15" s="17">
+        <v>1</v>
+      </c>
+      <c r="I15" s="17">
+        <v>1</v>
+      </c>
+      <c r="J15" s="17">
+        <v>1</v>
+      </c>
+      <c r="K15" s="17">
+        <v>1</v>
+      </c>
+      <c r="L15" s="17">
+        <v>1</v>
+      </c>
+      <c r="O15" s="17">
         <v>2</v>
       </c>
-      <c r="O15" s="19">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="19">
-        <v>1</v>
-      </c>
-      <c r="R15" s="19">
-        <v>1</v>
-      </c>
-      <c r="S15" s="19">
-        <v>1</v>
-      </c>
-      <c r="V15" s="19">
-        <v>1</v>
-      </c>
-      <c r="W15" s="19">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:29" ht="14">
+      <c r="P15" s="17">
+        <v>1</v>
+      </c>
+      <c r="R15" s="17">
+        <v>1</v>
+      </c>
+      <c r="S15" s="17">
+        <v>1</v>
+      </c>
+      <c r="T15" s="17">
+        <v>1</v>
+      </c>
+      <c r="W15" s="17">
+        <v>1</v>
+      </c>
+      <c r="X15" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" ht="14">
       <c r="A16">
         <v>10</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="16" t="s">
         <v>80</v>
       </c>
       <c r="C16" t="s">
         <v>81</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D16" s="14">
         <v>29625816</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="20"/>
-      <c r="Y16" s="24"/>
-    </row>
-    <row r="17" spans="1:25" ht="14">
+      <c r="E16" s="27" t="inlineStr">
+        <is>
+          <t>20211110620</t>
+        </is>
+      </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="18">
+        <v>1</v>
+      </c>
+      <c r="R16" s="18"/>
+      <c r="S16" s="18"/>
+      <c r="T16" s="18"/>
+      <c r="W16" s="18"/>
+      <c r="X16" s="18"/>
+      <c r="Z16" s="22"/>
+    </row>
+    <row r="17" spans="1:26" ht="14">
       <c r="A17">
         <v>11</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="15" t="s">
         <v>82</v>
       </c>
       <c r="C17" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="13">
         <v>28058651</v>
       </c>
-      <c r="E17" s="19">
-        <v>1</v>
-      </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="19"/>
-      <c r="S17" s="19"/>
-      <c r="V17" s="19"/>
-      <c r="W17" s="19"/>
-      <c r="Y17" s="23"/>
-    </row>
-    <row r="18" spans="1:25" ht="14">
+      <c r="E17" s="26" t="inlineStr">
+        <is>
+          <t>20211110025</t>
+        </is>
+      </c>
+      <c r="F17" s="17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="17"/>
+      <c r="L17" s="17"/>
+      <c r="O17" s="17"/>
+      <c r="P17" s="17"/>
+      <c r="R17" s="17"/>
+      <c r="S17" s="17"/>
+      <c r="T17" s="17"/>
+      <c r="W17" s="17"/>
+      <c r="X17" s="17"/>
+      <c r="Z17" s="21"/>
+    </row>
+    <row r="18" spans="1:26" ht="14">
       <c r="A18">
         <v>12</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="16" t="s">
         <v>84</v>
       </c>
       <c r="C18" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="16">
+      <c r="D18" s="14">
         <v>30358221</v>
       </c>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20">
-        <v>1</v>
-      </c>
-      <c r="I18" s="20">
-        <v>1</v>
-      </c>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20">
-        <v>1</v>
-      </c>
-      <c r="N18" s="20"/>
-      <c r="O18" s="20"/>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20">
-        <v>1</v>
-      </c>
-      <c r="S18" s="20"/>
-      <c r="V18" s="20"/>
-      <c r="W18" s="20"/>
-      <c r="Y18" s="24"/>
-    </row>
-    <row r="19" spans="1:25" ht="14">
+      <c r="E18" s="27" t="inlineStr">
+        <is>
+          <t>20231110030</t>
+        </is>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18">
+        <v>1</v>
+      </c>
+      <c r="J18" s="18">
+        <v>1</v>
+      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18">
+        <v>1</v>
+      </c>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="18">
+        <v>1</v>
+      </c>
+      <c r="T18" s="18"/>
+      <c r="W18" s="18"/>
+      <c r="X18" s="18"/>
+      <c r="Z18" s="22"/>
+    </row>
+    <row r="19" spans="1:26" ht="14">
       <c r="A19">
         <v>13</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C19" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="13">
         <v>30932824</v>
       </c>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19">
-        <v>1</v>
-      </c>
-      <c r="G19" s="19">
-        <v>1</v>
-      </c>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19">
-        <v>1</v>
-      </c>
-      <c r="K19" s="19">
-        <v>1</v>
-      </c>
-      <c r="N19" s="19">
+      <c r="E19" s="26" t="inlineStr">
+        <is>
+          <t>20231110616</t>
+        </is>
+      </c>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17">
+        <v>1</v>
+      </c>
+      <c r="H19" s="17">
+        <v>1</v>
+      </c>
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+      <c r="K19" s="17">
+        <v>1</v>
+      </c>
+      <c r="L19" s="17">
+        <v>1</v>
+      </c>
+      <c r="O19" s="17">
         <v>2</v>
       </c>
-      <c r="O19" s="19">
-        <v>1</v>
-      </c>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="19"/>
-      <c r="S19" s="19">
-        <v>1</v>
-      </c>
-      <c r="V19" s="19"/>
-      <c r="W19" s="19"/>
-      <c r="Y19" s="23"/>
-    </row>
-    <row r="20" spans="1:25" ht="14">
+      <c r="P19" s="17">
+        <v>1</v>
+      </c>
+      <c r="R19" s="17"/>
+      <c r="S19" s="17"/>
+      <c r="T19" s="17">
+        <v>1</v>
+      </c>
+      <c r="W19" s="17"/>
+      <c r="X19" s="17"/>
+      <c r="Z19" s="21"/>
+    </row>
+    <row r="20" spans="1:26" ht="14">
       <c r="A20">
         <v>14</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="16" t="s">
         <v>88</v>
       </c>
       <c r="C20" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="16">
+      <c r="D20" s="14">
         <v>30687748</v>
       </c>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-      <c r="V20" s="20"/>
-      <c r="W20" s="20"/>
-      <c r="Y20" s="24"/>
-    </row>
-    <row r="21" spans="1:25" ht="14">
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>20221110413</t>
+        </is>
+      </c>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="18"/>
+      <c r="R20" s="18"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="18"/>
+      <c r="W20" s="18"/>
+      <c r="X20" s="18"/>
+      <c r="Z20" s="22"/>
+    </row>
+    <row r="21" spans="1:26" ht="14">
       <c r="A21">
         <v>15</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="15" t="s">
         <v>90</v>
       </c>
       <c r="C21" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="15">
+      <c r="D21" s="13">
         <v>29577475</v>
       </c>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19">
-        <v>1</v>
-      </c>
-      <c r="H21" s="19">
-        <v>1</v>
-      </c>
-      <c r="I21" s="19">
-        <v>1</v>
-      </c>
-      <c r="J21" s="19">
+      <c r="E21" s="26" t="inlineStr">
+        <is>
+          <t>20211110857</t>
+        </is>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17">
+        <v>1</v>
+      </c>
+      <c r="I21" s="17">
+        <v>1</v>
+      </c>
+      <c r="J21" s="17">
+        <v>1</v>
+      </c>
+      <c r="K21" s="17">
         <v>2</v>
       </c>
-      <c r="K21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="Q21" s="19"/>
-      <c r="R21" s="19"/>
-      <c r="S21" s="19"/>
-      <c r="V21" s="19"/>
-      <c r="W21" s="19"/>
-      <c r="Y21" s="23"/>
-    </row>
-    <row r="22" spans="1:25" ht="14">
+      <c r="L21" s="17"/>
+      <c r="O21" s="17"/>
+      <c r="P21" s="17"/>
+      <c r="R21" s="17"/>
+      <c r="S21" s="17"/>
+      <c r="T21" s="17"/>
+      <c r="W21" s="17"/>
+      <c r="X21" s="17"/>
+      <c r="Z21" s="21"/>
+    </row>
+    <row r="22" spans="1:26" ht="14">
       <c r="A22">
         <v>16</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="16" t="s">
         <v>92</v>
       </c>
       <c r="C22" t="s">
         <v>93</v>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="14">
         <v>30821945</v>
       </c>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
-      <c r="V22" s="20"/>
-      <c r="W22" s="20"/>
-      <c r="Y22" s="24"/>
-    </row>
-    <row r="23" spans="1:25" ht="14">
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>20231110297</t>
+        </is>
+      </c>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="18"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="W22" s="18"/>
+      <c r="X22" s="18"/>
+      <c r="Z22" s="22"/>
+    </row>
+    <row r="23" spans="1:26" ht="14">
       <c r="A23">
         <v>17</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="15" t="s">
         <v>94</v>
       </c>
       <c r="C23" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="15">
+      <c r="D23" s="13">
         <v>24843496</v>
       </c>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="19"/>
-      <c r="K23" s="19"/>
-      <c r="N23" s="19"/>
-      <c r="O23" s="19"/>
-      <c r="Q23" s="19"/>
-      <c r="R23" s="19"/>
-      <c r="S23" s="19"/>
-      <c r="V23" s="19"/>
-      <c r="W23" s="19"/>
-      <c r="Y23" s="23"/>
-    </row>
-    <row r="24" spans="1:25" ht="14">
+      <c r="E23" s="26" t="inlineStr">
+        <is>
+          <t>20221120086</t>
+        </is>
+      </c>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
+      <c r="O23" s="17"/>
+      <c r="P23" s="17"/>
+      <c r="R23" s="17"/>
+      <c r="S23" s="17"/>
+      <c r="T23" s="17"/>
+      <c r="W23" s="17"/>
+      <c r="X23" s="17"/>
+      <c r="Z23" s="21"/>
+    </row>
+    <row r="24" spans="1:26" ht="14">
       <c r="A24">
         <v>18</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="16" t="s">
         <v>96</v>
       </c>
       <c r="C24" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="14">
         <v>30497106</v>
       </c>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20">
-        <v>1</v>
-      </c>
-      <c r="J24" s="20">
-        <v>1</v>
-      </c>
-      <c r="K24" s="20">
-        <v>1</v>
-      </c>
-      <c r="N24" s="20">
-        <v>1</v>
-      </c>
-      <c r="O24" s="20">
-        <v>1</v>
-      </c>
-      <c r="Q24" s="20">
-        <v>1</v>
-      </c>
-      <c r="R24" s="20">
-        <v>1</v>
-      </c>
-      <c r="S24" s="20">
+      <c r="E24" s="27" t="inlineStr">
+        <is>
+          <t>20231110512</t>
+        </is>
+      </c>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
+      <c r="J24" s="18">
+        <v>1</v>
+      </c>
+      <c r="K24" s="18">
+        <v>1</v>
+      </c>
+      <c r="L24" s="18">
+        <v>1</v>
+      </c>
+      <c r="O24" s="18">
+        <v>1</v>
+      </c>
+      <c r="P24" s="18">
+        <v>1</v>
+      </c>
+      <c r="R24" s="18">
+        <v>1</v>
+      </c>
+      <c r="S24" s="18">
+        <v>1</v>
+      </c>
+      <c r="T24" s="18">
         <v>3</v>
       </c>
-      <c r="V24" s="20">
-        <v>1</v>
-      </c>
-      <c r="W24" s="20">
-        <v>1</v>
-      </c>
-      <c r="Y24" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" ht="14">
+      <c r="W24" s="18">
+        <v>1</v>
+      </c>
+      <c r="X24" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" ht="14">
       <c r="A25">
         <v>19</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="15" t="s">
         <v>98</v>
       </c>
       <c r="C25" t="s">
         <v>99</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="13">
         <v>29948276</v>
       </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="N25" s="19"/>
-      <c r="O25" s="19"/>
-      <c r="Q25" s="19">
-        <v>1</v>
-      </c>
-      <c r="R25" s="19"/>
-      <c r="S25" s="19"/>
-      <c r="V25" s="19">
-        <v>1</v>
-      </c>
-      <c r="W25" s="19"/>
-      <c r="Y25" s="23"/>
-    </row>
-    <row r="26" spans="1:25" ht="14">
+      <c r="E25" s="26" t="inlineStr">
+        <is>
+          <t>20221130009</t>
+        </is>
+      </c>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="O25" s="17"/>
+      <c r="P25" s="17"/>
+      <c r="R25" s="17">
+        <v>1</v>
+      </c>
+      <c r="S25" s="17"/>
+      <c r="T25" s="17"/>
+      <c r="W25" s="17">
+        <v>1</v>
+      </c>
+      <c r="X25" s="17"/>
+      <c r="Z25" s="21"/>
+    </row>
+    <row r="26" spans="1:26" ht="14">
       <c r="A26">
         <v>20</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="16" t="s">
         <v>100</v>
       </c>
       <c r="C26" t="s">
         <v>101</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="14">
         <v>30612888</v>
       </c>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20">
-        <v>1</v>
-      </c>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20">
+      <c r="E26" s="27" t="inlineStr">
+        <is>
+          <t>20231110449</t>
+        </is>
+      </c>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18">
+        <v>1</v>
+      </c>
+      <c r="I26" s="18"/>
+      <c r="J26" s="18">
         <v>2</v>
       </c>
-      <c r="J26" s="20">
-        <v>1</v>
-      </c>
-      <c r="K26" s="20">
-        <v>1</v>
-      </c>
-      <c r="N26" s="20">
+      <c r="K26" s="18">
+        <v>1</v>
+      </c>
+      <c r="L26" s="18">
+        <v>1</v>
+      </c>
+      <c r="O26" s="18">
         <v>2</v>
       </c>
-      <c r="O26" s="20"/>
-      <c r="Q26" s="20">
-        <v>1</v>
-      </c>
-      <c r="R26" s="20">
-        <v>1</v>
-      </c>
-      <c r="S26" s="20">
-        <v>1</v>
-      </c>
-      <c r="V26" s="20">
-        <v>1</v>
-      </c>
-      <c r="W26" s="20">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" ht="14">
+      <c r="P26" s="18"/>
+      <c r="R26" s="18">
+        <v>1</v>
+      </c>
+      <c r="S26" s="18">
+        <v>1</v>
+      </c>
+      <c r="T26" s="18">
+        <v>1</v>
+      </c>
+      <c r="W26" s="18">
+        <v>1</v>
+      </c>
+      <c r="X26" s="18">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" ht="14">
       <c r="A27">
         <v>21</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="15" t="s">
         <v>102</v>
       </c>
       <c r="C27" t="s">
         <v>103</v>
       </c>
-      <c r="D27" s="15">
+      <c r="D27" s="13">
         <v>29533663</v>
       </c>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="N27" s="19"/>
-      <c r="O27" s="19"/>
-      <c r="Q27" s="19"/>
-      <c r="R27" s="19"/>
-      <c r="S27" s="19"/>
-      <c r="V27" s="19"/>
-      <c r="W27" s="19"/>
-      <c r="Y27" s="23"/>
-    </row>
-    <row r="28" spans="1:25" ht="14">
+      <c r="E27" s="26" t="inlineStr">
+        <is>
+          <t>20201130038</t>
+        </is>
+      </c>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+      <c r="K27" s="17"/>
+      <c r="L27" s="17"/>
+      <c r="O27" s="17"/>
+      <c r="P27" s="17"/>
+      <c r="R27" s="17"/>
+      <c r="S27" s="17"/>
+      <c r="T27" s="17"/>
+      <c r="W27" s="17"/>
+      <c r="X27" s="17"/>
+      <c r="Z27" s="21"/>
+    </row>
+    <row r="28" spans="1:26" ht="14">
       <c r="A28">
         <v>22</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="16" t="s">
         <v>104</v>
       </c>
       <c r="C28" t="s">
         <v>105</v>
       </c>
-      <c r="D28" s="16">
+      <c r="D28" s="14">
         <v>30142697</v>
       </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20">
-        <v>1</v>
-      </c>
-      <c r="K28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="Q28" s="20"/>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="20"/>
-      <c r="Y28" s="24"/>
-    </row>
-    <row r="29" spans="1:25" ht="14">
+      <c r="E28" s="27" t="inlineStr">
+        <is>
+          <t>20221110475</t>
+        </is>
+      </c>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18">
+        <v>1</v>
+      </c>
+      <c r="L28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="18"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="18"/>
+      <c r="T28" s="18"/>
+      <c r="W28" s="18"/>
+      <c r="X28" s="18"/>
+      <c r="Z28" s="22"/>
+    </row>
+    <row r="29" spans="1:26" ht="14">
       <c r="A29">
         <v>23</v>
       </c>
-      <c r="B29" s="17" t="s">
+      <c r="B29" s="15" t="s">
         <v>106</v>
       </c>
       <c r="C29" t="s">
         <v>107</v>
       </c>
-      <c r="D29" s="15">
+      <c r="D29" s="13">
         <v>19820976</v>
       </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="19"/>
-      <c r="J29" s="19"/>
-      <c r="K29" s="19"/>
-      <c r="N29" s="19"/>
-      <c r="O29" s="19"/>
-      <c r="Q29" s="19"/>
-      <c r="R29" s="19"/>
-      <c r="S29" s="19"/>
-      <c r="V29" s="19"/>
-      <c r="W29" s="19"/>
-      <c r="Y29" s="23"/>
-    </row>
-    <row r="30" spans="1:25" ht="14">
+      <c r="E29" s="26" t="inlineStr">
+        <is>
+          <t>200865920</t>
+        </is>
+      </c>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
+      <c r="O29" s="17"/>
+      <c r="P29" s="17"/>
+      <c r="R29" s="17"/>
+      <c r="S29" s="17"/>
+      <c r="T29" s="17"/>
+      <c r="W29" s="17"/>
+      <c r="X29" s="17"/>
+      <c r="Z29" s="21"/>
+    </row>
+    <row r="30" spans="1:26" ht="14">
       <c r="A30">
         <v>24</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="16" t="s">
         <v>108</v>
       </c>
       <c r="C30" t="s">
         <v>109</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="14">
         <v>30142131</v>
       </c>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="N30" s="20"/>
-      <c r="O30" s="20"/>
-      <c r="Q30" s="20"/>
-      <c r="R30" s="20"/>
-      <c r="S30" s="20"/>
-      <c r="V30" s="20"/>
-      <c r="W30" s="20"/>
-      <c r="Y30" s="24"/>
-    </row>
-    <row r="31" spans="1:25" ht="14">
+      <c r="E30" s="27" t="inlineStr">
+        <is>
+          <t>20221110193</t>
+        </is>
+      </c>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18"/>
+      <c r="L30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="18"/>
+      <c r="R30" s="18"/>
+      <c r="S30" s="18"/>
+      <c r="T30" s="18"/>
+      <c r="W30" s="18"/>
+      <c r="X30" s="18"/>
+      <c r="Z30" s="22"/>
+    </row>
+    <row r="31" spans="1:26" ht="14">
       <c r="A31">
         <v>25</v>
       </c>
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="15" t="s">
         <v>110</v>
       </c>
       <c r="C31" t="s">
         <v>111</v>
       </c>
-      <c r="D31" s="15">
+      <c r="D31" s="13">
         <v>29965689</v>
       </c>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19">
-        <v>1</v>
-      </c>
-      <c r="K31" s="19"/>
-      <c r="N31" s="19"/>
-      <c r="O31" s="19"/>
-      <c r="Q31" s="19"/>
-      <c r="R31" s="19"/>
-      <c r="S31" s="19"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="19"/>
-      <c r="Y31" s="23"/>
-    </row>
-    <row r="32" spans="1:25" ht="14">
+      <c r="E31" s="26" t="inlineStr">
+        <is>
+          <t>20221110437</t>
+        </is>
+      </c>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+      <c r="K31" s="17">
+        <v>1</v>
+      </c>
+      <c r="L31" s="17"/>
+      <c r="O31" s="17"/>
+      <c r="P31" s="17"/>
+      <c r="R31" s="17"/>
+      <c r="S31" s="17"/>
+      <c r="T31" s="17"/>
+      <c r="W31" s="17"/>
+      <c r="X31" s="17"/>
+      <c r="Z31" s="21"/>
+    </row>
+    <row r="32" spans="1:26" ht="14">
       <c r="A32">
         <v>26</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="16" t="s">
         <v>112</v>
       </c>
       <c r="C32" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="14">
         <v>27790060</v>
       </c>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20">
-        <v>1</v>
-      </c>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="N32" s="20"/>
-      <c r="O32" s="20"/>
-      <c r="Q32" s="20"/>
-      <c r="R32" s="20"/>
-      <c r="S32" s="20"/>
-      <c r="V32" s="20"/>
-      <c r="W32" s="20"/>
-      <c r="Y32" s="24"/>
-    </row>
-    <row r="33" spans="1:25" ht="14">
+      <c r="E32" s="27" t="inlineStr">
+        <is>
+          <t>20191110205</t>
+        </is>
+      </c>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
+      <c r="J32" s="18">
+        <v>1</v>
+      </c>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="18"/>
+      <c r="R32" s="18"/>
+      <c r="S32" s="18"/>
+      <c r="T32" s="18"/>
+      <c r="W32" s="18"/>
+      <c r="X32" s="18"/>
+      <c r="Z32" s="22"/>
+    </row>
+    <row r="33" spans="1:26" ht="14">
       <c r="A33">
         <v>27</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="15" t="s">
         <v>114</v>
       </c>
       <c r="C33" t="s">
         <v>115</v>
       </c>
-      <c r="D33" s="15">
+      <c r="D33" s="13">
         <v>30124022</v>
       </c>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="19"/>
-      <c r="K33" s="19"/>
-      <c r="N33" s="19"/>
-      <c r="O33" s="19"/>
-      <c r="Q33" s="19"/>
-      <c r="R33" s="19"/>
-      <c r="S33" s="19"/>
-      <c r="V33" s="19"/>
-      <c r="W33" s="19"/>
-      <c r="Y33" s="23"/>
-    </row>
-    <row r="34" spans="1:25" ht="14">
+      <c r="E33" s="26" t="inlineStr">
+        <is>
+          <t>20221110061</t>
+        </is>
+      </c>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
+      <c r="L33" s="17"/>
+      <c r="O33" s="17"/>
+      <c r="P33" s="17"/>
+      <c r="R33" s="17"/>
+      <c r="S33" s="17"/>
+      <c r="T33" s="17"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Z33" s="21"/>
+    </row>
+    <row r="34" spans="1:26" ht="14">
       <c r="A34">
         <v>28</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="16" t="s">
         <v>116</v>
       </c>
       <c r="C34" t="s">
         <v>117</v>
       </c>
-      <c r="D34" s="16">
+      <c r="D34" s="14">
         <v>28317519</v>
       </c>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="N34" s="20"/>
-      <c r="O34" s="20"/>
-      <c r="Q34" s="20"/>
-      <c r="R34" s="20"/>
-      <c r="S34" s="20"/>
-      <c r="V34" s="20"/>
-      <c r="W34" s="20"/>
-      <c r="Y34" s="24"/>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>20191110269</t>
+        </is>
+      </c>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="18"/>
+      <c r="R34" s="18"/>
+      <c r="S34" s="18"/>
+      <c r="T34" s="18"/>
+      <c r="W34" s="18"/>
+      <c r="X34" s="18"/>
+      <c r="Z34" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Y5:Z5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
+  <mergeCells count="17">
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Datos Tesis Upstream/Computacion Emergente/2526-1/Particip emergente 2526-1.xlsx
+++ b/Datos Tesis Upstream/Computacion Emergente/2526-1/Particip emergente 2526-1.xlsx
@@ -15,6 +15,7 @@
   <sheets>
     <sheet name="Intervenciones" sheetId="2" r:id="rId1"/>
     <sheet name="Estandar" sheetId="3" r:id="rId2"/>
+    <sheet name="Cronograma" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4116,4 +4117,360 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dia_sesion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">administrativa</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema = código del catálogo de la asignatura. Si la sesión no cubre contenido nuevo: tema = 0 y tipo_sesion indica la causa (evaluacion, repaso, sin_clase, administrativa). Si tema &gt; 0 la sesión es de contenido y tipo_sesion queda vacío.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/Datos Tesis Upstream/Computacion Emergente/2526-1/Particip emergente 2526-1.xlsx
+++ b/Datos Tesis Upstream/Computacion Emergente/2526-1/Particip emergente 2526-1.xlsx
@@ -4191,7 +4191,7 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -4202,7 +4202,7 @@
         <v>1</v>
       </c>
       <c r="C6">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -4213,7 +4213,7 @@
         <v>2</v>
       </c>
       <c r="C7">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4224,7 +4224,7 @@
         <v>1</v>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -4267,7 +4267,7 @@
         <v>2</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -4278,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="C12">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -4305,7 +4305,7 @@
         <v>1</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -4316,7 +4316,7 @@
         <v>2</v>
       </c>
       <c r="C15">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4327,7 +4327,7 @@
         <v>1</v>
       </c>
       <c r="C16">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -4370,7 +4370,7 @@
         <v>2</v>
       </c>
       <c r="C19">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -4381,7 +4381,7 @@
         <v>1</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -4408,7 +4408,7 @@
         <v>1</v>
       </c>
       <c r="C22">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
